--- a/data/trans_bre/P2A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 4,58</t>
+          <t>-16,35; 3,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 10,84</t>
+          <t>-11,14; 11,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 14,34</t>
+          <t>-9,32; 14,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 27,55</t>
+          <t>-2,75; 28,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 16,88</t>
+          <t>-42,23; 12,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 36,92</t>
+          <t>-26,51; 40,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 57,79</t>
+          <t>-26,34; 58,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 53,72</t>
+          <t>-3,59; 54,3</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 3,23</t>
+          <t>-14,77; 2,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 6,41</t>
+          <t>-11,96; 6,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 7,03</t>
+          <t>-10,25; 6,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 7,28</t>
+          <t>-10,41; 7,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,73; 9,88</t>
+          <t>-36,62; 7,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 17,33</t>
+          <t>-28,15; 19,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 22,97</t>
+          <t>-25,38; 19,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 10,35</t>
+          <t>-13,39; 10,01</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 7,14</t>
+          <t>-13,33; 5,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 7,48</t>
+          <t>-11,44; 8,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 5,84</t>
+          <t>-14,4; 4,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 13,4</t>
+          <t>-4,78; 13,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 19,38</t>
+          <t>-29,06; 14,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 26,03</t>
+          <t>-28,77; 30,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,98; 19,71</t>
+          <t>-37,82; 15,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 18,55</t>
+          <t>-6,03; 18,34</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 5,41</t>
+          <t>-12,39; 5,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 14,79</t>
+          <t>-3,76; 15,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 14,3</t>
+          <t>-3,06; 14,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 5,94</t>
+          <t>-8,47; 5,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 17,04</t>
+          <t>-30,03; 15,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 56,4</t>
+          <t>-10,74; 54,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 51,0</t>
+          <t>-9,47; 48,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 7,61</t>
+          <t>-10,07; 7,36</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 0,33</t>
+          <t>-9,33; -0,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 5,1</t>
+          <t>-4,85; 4,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 5,22</t>
+          <t>-4,17; 5,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 7,67</t>
+          <t>-2,63; 7,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 1,02</t>
+          <t>-23,34; -0,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 15,46</t>
+          <t>-12,81; 14,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 16,36</t>
+          <t>-11,57; 17,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 10,43</t>
+          <t>-3,38; 10,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 3,64</t>
+          <t>-16,45; 3,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 11,82</t>
+          <t>-10,67; 11,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 14,39</t>
+          <t>-9,6; 13,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 28,16</t>
+          <t>-2,03; 25,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 12,03</t>
+          <t>-42,85; 11,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,51; 40,39</t>
+          <t>-26,99; 37,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,34; 58,56</t>
+          <t>-26,69; 53,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 54,3</t>
+          <t>-2,66; 47,89</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 2,87</t>
+          <t>-15,84; 2,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 6,61</t>
+          <t>-11,44; 6,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 6,22</t>
+          <t>-10,03; 6,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 7,17</t>
+          <t>-10,42; 7,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,62; 7,99</t>
+          <t>-37,84; 7,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,15; 19,91</t>
+          <t>-26,63; 20,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 19,25</t>
+          <t>-25,29; 19,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 10,01</t>
+          <t>-13,49; 10,6</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 5,56</t>
+          <t>-13,61; 7,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 8,4</t>
+          <t>-11,18; 8,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 4,51</t>
+          <t>-13,77; 4,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 13,42</t>
+          <t>-4,63; 13,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 14,91</t>
+          <t>-29,42; 18,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 30,7</t>
+          <t>-29,04; 30,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-37,82; 15,67</t>
+          <t>-36,1; 16,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 18,34</t>
+          <t>-5,82; 18,61</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 5,18</t>
+          <t>-12,25; 4,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 15,02</t>
+          <t>-3,68; 14,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 14,1</t>
+          <t>-3,37; 14,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 5,72</t>
+          <t>-8,77; 5,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,03; 15,98</t>
+          <t>-29,68; 16,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 54,4</t>
+          <t>-10,27; 55,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 48,58</t>
+          <t>-8,99; 48,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 7,36</t>
+          <t>-10,51; 7,4</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; -0,18</t>
+          <t>-8,94; 0,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 4,83</t>
+          <t>-4,79; 5,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 5,38</t>
+          <t>-3,83; 5,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 7,88</t>
+          <t>-2,77; 7,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,34; -0,03</t>
+          <t>-22,7; 1,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 14,58</t>
+          <t>-12,64; 16,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 17,29</t>
+          <t>-10,79; 18,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 10,85</t>
+          <t>-3,51; 10,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,43</t>
+          <t>5,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 3,45</t>
+          <t>-15,93; 4,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 11,13</t>
+          <t>-12,03; 10,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 13,1</t>
+          <t>-8,48; 14,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 25,52</t>
+          <t>-4,45; 22,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-42,85; 11,81</t>
+          <t>-41,86; 16,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 37,09</t>
+          <t>-30,1; 36,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,69; 53,26</t>
+          <t>-23,67; 57,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 47,89</t>
+          <t>-5,59; 39,2</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-1,56%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 2,45</t>
+          <t>-14,84; 3,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 6,78</t>
+          <t>-11,36; 6,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 6,06</t>
+          <t>-9,09; 7,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 7,46</t>
+          <t>-7,61; 8,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 7,71</t>
+          <t>-36,73; 9,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,63; 20,13</t>
+          <t>-27,24; 17,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 19,26</t>
+          <t>-23,86; 22,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-13,49; 10,6</t>
+          <t>-9,54; 11,51</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>-1,1%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 7,02</t>
+          <t>-13,27; 7,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 8,8</t>
+          <t>-11,82; 7,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 4,71</t>
+          <t>-13,47; 5,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 13,82</t>
+          <t>-8,96; 7,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 18,81</t>
+          <t>-27,77; 19,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,04; 30,86</t>
+          <t>-30,61; 26,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,1; 16,23</t>
+          <t>-34,98; 19,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 18,61</t>
+          <t>-11,15; 10,65</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-1,96</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-1,78%</t>
+          <t>-2,39%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 4,89</t>
+          <t>-12,29; 5,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 14,99</t>
+          <t>-3,63; 14,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 14,22</t>
+          <t>-3,33; 14,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 5,88</t>
+          <t>-9,49; 5,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 16,21</t>
+          <t>-29,48; 17,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 55,59</t>
+          <t>-10,37; 56,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 48,83</t>
+          <t>-9,78; 51,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 7,4</t>
+          <t>-11,15; 6,84</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 0,45</t>
+          <t>-9,27; 0,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 5,31</t>
+          <t>-4,78; 5,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 5,72</t>
+          <t>-4,09; 5,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 7,81</t>
+          <t>-3,56; 5,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,7; 1,33</t>
+          <t>-23,54; 1,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 16,28</t>
+          <t>-12,67; 15,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 18,44</t>
+          <t>-11,5; 16,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 10,78</t>
+          <t>-4,55; 6,81</t>
         </is>
       </c>
     </row>
